--- a/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
+++ b/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="Ra37e1773392a4ac1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R69358c703ded405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="Rd7b068c4711b4012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="R16bfbfbe16674c03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="Rd0a28e22007a4e56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="R06b06f1540f8494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="7" r:id="R289031306aed49e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="8" r:id="R95fb52b2d8a44280"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="Rafba1ea1172f4742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R828e1e47371b44d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="Rf060d033ab8b4cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="Rbabe3e8423fd40c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="Rc3df9c2420774152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="R0a703cd380f64823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R00d98201f98e425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="8" r:id="Rcfe3092ac7f547a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="9" r:id="R0317d9d6495d4e82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0.00"/>
     <x:numFmt numFmtId="201" formatCode="0.00%"/>
+    <x:numFmt numFmtId="202" formatCode="0.000000"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -65,7 +67,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -79,6 +81,7 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -602,7 +605,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fc98f063d364147"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf43eb5999104e7c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -637,7 +640,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R322069b5f0044761"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R178afdc091d14d98"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -648,7 +651,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{E8600CFB-3307-4A0E-956C-BAB42A36210C}"/>
+  <xltc:person displayName="User" id="{7879DC63-B7A0-4CD9-9467-94FD332062FF}"/>
 </xltc:personList>
 </file>
 
@@ -904,7 +907,7 @@
         <x:v>区间设计</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>基准区间排除2020极端残差；压力区间保留2020极端残差</x:v>
+        <x:v>基准区间排除2020极端残差后重新中心化；压力区间保留全部残差并中心化</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
@@ -1814,10 +1817,10 @@
         <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="E2" s="7" t="n">
-        <x:v>2487.2823450036813</x:v>
+        <x:v>2401.8353068406677</x:v>
       </x:c>
       <x:c r="F2" s="7" t="n">
-        <x:v>3486.241273584903</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="G2" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -1840,10 +1843,10 @@
         <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="E3" s="7" t="n">
-        <x:v>2608.182469911016</x:v>
+        <x:v>2432.0597844187496</x:v>
       </x:c>
       <x:c r="F3" s="7" t="n">
-        <x:v>4183.489528301885</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="G3" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -1866,10 +1869,10 @@
         <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="E4" s="7" t="n">
-        <x:v>2797.3125914708403</x:v>
+        <x:v>2518.810021322432</x:v>
       </x:c>
       <x:c r="F4" s="7" t="n">
-        <x:v>5020.187433962272</x:v>
+        <x:v>4520.373753057168</x:v>
       </x:c>
       <x:c r="G4" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -1892,10 +1895,10 @@
         <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="E5" s="7" t="n">
-        <x:v>2970.215415374755</x:v>
+        <x:v>2582.6199260176004</x:v>
       </x:c>
       <x:c r="F5" s="7" t="n">
-        <x:v>5861.408031004597</x:v>
+        <x:v>5096.529058813096</x:v>
       </x:c>
       <x:c r="G5" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -1918,10 +1921,10 @@
         <x:v>3954.452041745783</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>3190.7437184649757</x:v>
+        <x:v>2679.0610483781643</x:v>
       </x:c>
       <x:c r="F6" s="7" t="n">
-        <x:v>6819.322401419462</x:v>
+        <x:v>5725.74378702051</x:v>
       </x:c>
       <x:c r="G6" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2074,10 +2077,10 @@
         <x:v>224.43130693451835</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>180.9954751131221</x:v>
+        <x:v>173.61813455540295</x:v>
       </x:c>
       <x:c r="F12" s="7" t="n">
-        <x:v>290.9090909090906</x:v>
+        <x:v>279.05169263086566</x:v>
       </x:c>
       <x:c r="G12" s="8" t="n">
         <x:v>0.11525231133777775</x:v>
@@ -2100,10 +2103,10 @@
         <x:v>251.84705766167988</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>197.70274973894882</x:v>
+        <x:v>181.91455386161562</x:v>
       </x:c>
       <x:c r="F13" s="7" t="n">
-        <x:v>363.6363636363632</x:v>
+        <x:v>334.5969995162747</x:v>
       </x:c>
       <x:c r="G13" s="8" t="n">
         <x:v>0.11525231133777775</x:v>
@@ -2126,10 +2129,10 @@
         <x:v>282.61182149311907</x:v>
       </x:c>
       <x:c r="E14" s="7" t="n">
-        <x:v>223.73579108229808</x:v>
+        <x:v>197.47747601548753</x:v>
       </x:c>
       <x:c r="F14" s="7" t="n">
-        <x:v>447.1153396824204</x:v>
+        <x:v>394.6405192534152</x:v>
       </x:c>
       <x:c r="G14" s="8" t="n">
         <x:v>0.11525231133777775</x:v>
@@ -2152,10 +2155,10 @@
         <x:v>317.1347022642276</x:v>
       </x:c>
       <x:c r="E15" s="7" t="n">
-        <x:v>244.1199170689629</x:v>
+        <x:v>206.68677347144515</x:v>
       </x:c>
       <x:c r="F15" s="7" t="n">
-        <x:v>552.155957512037</x:v>
+        <x:v>467.48882549783883</x:v>
       </x:c>
       <x:c r="G15" s="8" t="n">
         <x:v>0.11525231133777775</x:v>
@@ -2178,10 +2181,10 @@
         <x:v>355.8747785172497</x:v>
       </x:c>
       <x:c r="E16" s="7" t="n">
-        <x:v>269.9853648717954</x:v>
+        <x:v>219.26891259334394</x:v>
       </x:c>
       <x:c r="F16" s="7" t="n">
-        <x:v>677.8389767662317</x:v>
+        <x:v>550.5076744418875</x:v>
       </x:c>
       <x:c r="G16" s="8" t="n">
         <x:v>0.11525231133777775</x:v>
@@ -2372,10 +2375,10 @@
         <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="D2" s="7" t="n">
-        <x:v>2487.2823450036813</x:v>
+        <x:v>2401.8353068406677</x:v>
       </x:c>
       <x:c r="E2" s="7" t="n">
-        <x:v>3486.241273584903</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="F2" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2395,10 +2398,10 @@
         <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="D3" s="7" t="n">
-        <x:v>2608.182469911016</x:v>
+        <x:v>2432.0597844187496</x:v>
       </x:c>
       <x:c r="E3" s="7" t="n">
-        <x:v>4183.489528301885</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="F3" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2418,10 +2421,10 @@
         <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="D4" s="7" t="n">
-        <x:v>2797.3125914708403</x:v>
+        <x:v>2518.810021322432</x:v>
       </x:c>
       <x:c r="E4" s="7" t="n">
-        <x:v>5020.187433962272</x:v>
+        <x:v>4520.373753057168</x:v>
       </x:c>
       <x:c r="F4" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2441,10 +2444,10 @@
         <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="D5" s="7" t="n">
-        <x:v>2970.215415374755</x:v>
+        <x:v>2582.6199260176004</x:v>
       </x:c>
       <x:c r="E5" s="7" t="n">
-        <x:v>5861.408031004597</x:v>
+        <x:v>5096.529058813096</x:v>
       </x:c>
       <x:c r="F5" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2464,10 +2467,10 @@
         <x:v>3954.452041745783</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
-        <x:v>3190.7437184649757</x:v>
+        <x:v>2679.0610483781643</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>6819.322401419462</x:v>
+        <x:v>5725.74378702051</x:v>
       </x:c>
       <x:c r="F6" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2487,10 +2490,10 @@
         <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="D7" s="7" t="n">
-        <x:v>2648.7252012645845</x:v>
+        <x:v>2557.732023988019</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>3486.241273584903</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="F7" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2510,10 +2513,10 @@
         <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="D8" s="7" t="n">
-        <x:v>2777.4726304904448</x:v>
+        <x:v>2589.91829170987</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>4183.489528301885</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="F8" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2533,10 +2536,10 @@
         <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="D9" s="7" t="n">
-        <x:v>2936.453728163701</x:v>
+        <x:v>2644.098160570357</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>4812.596101139612</x:v>
+        <x:v>4333.450371291507</x:v>
       </x:c>
       <x:c r="F9" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2556,10 +2559,10 @@
         <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="D10" s="7" t="n">
-        <x:v>3178.949376563837</x:v>
+        <x:v>2764.1153436944014</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>5640.0053710428765</x:v>
+        <x:v>4904.018132389836</x:v>
       </x:c>
       <x:c r="F10" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2579,10 +2582,10 @@
         <x:v>3954.452041745783</x:v>
       </x:c>
       <x:c r="D11" s="7" t="n">
-        <x:v>3436.574740799046</x:v>
+        <x:v>2885.469451725281</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>6519.536596211016</x:v>
+        <x:v>5474.033043552513</x:v>
       </x:c>
       <x:c r="F11" s="8" t="n">
         <x:v>0.07698583432900019</x:v>
@@ -2779,137 +2782,116 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>年份</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>点预测</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>基准下界</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>基准上界</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>压力下界</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>压力上界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="B2" t="n">
-        <x:v>2906.3520568538356</x:v>
-      </x:c>
-      <x:c r="C2" t="n">
-        <x:v>2487.2823450036813</x:v>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>scenario</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>removed_2020</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>residual_count</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>residual_mean_before_centering</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>residual_mean_after_centering</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>baseline</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>True</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>3486.241273584903</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>1781.5669392857153</x:v>
-      </x:c>
-      <x:c r="F2" t="n">
-        <x:v>3486.241273584903</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>2027</x:v>
-      </x:c>
-      <x:c r="B3" t="n">
-        <x:v>3138.93804473375</x:v>
-      </x:c>
-      <x:c r="C3" t="n">
-        <x:v>2608.182469911016</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>0.03495753043140638</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>4.956352788505163e-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>stress</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>False</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>4183.489528301885</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>1868.164130763831</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>4183.489528301885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>2028</x:v>
-      </x:c>
-      <x:c r="B4" t="n">
-        <x:v>3390.13713959446</x:v>
-      </x:c>
-      <x:c r="C4" t="n">
-        <x:v>2797.3125914708403</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>baseline</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>True</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>5020.187433962272</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>1846.8652682262345</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>4982.8637832413215</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>2029</x:v>
-      </x:c>
-      <x:c r="B5" t="n">
-        <x:v>3661.438888397227</x:v>
-      </x:c>
-      <x:c r="C5" t="n">
-        <x:v>2970.215415374755</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="n">
+        <x:v>0.04161377308314497</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="n">
+        <x:v>-3.96508223080413e-18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>stress</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>False</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>5861.408031004597</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>1757.8226777328273</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>5751.407153362984</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>2030</x:v>
-      </x:c>
-      <x:c r="B6" t="n">
-        <x:v>3954.452041745783</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>3190.7437184649757</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>6819.322401419462</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>1711.7519715612111</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>6635.556261514627</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>7.401486830834377e-18</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>7.401486830834377e-18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeab4712fab54692"/>
 </x:worksheet>
 </file>
 
@@ -2950,19 +2932,19 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>224.43130693451835</x:v>
+        <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>180.9954751131221</x:v>
+        <x:v>2401.8353068406677</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>290.9090909090906</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>125.33333333333331</x:v>
+        <x:v>1781.5669392857153</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>290.9090909090906</x:v>
+        <x:v>3486.241273584903</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2970,19 +2952,19 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>251.84705766167988</x:v>
+        <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>197.70274973894882</x:v>
+        <x:v>2432.0597844187496</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>363.6363636363632</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>136.90256410256413</x:v>
+        <x:v>1868.164130763831</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>353.566433566433</x:v>
+        <x:v>4183.489528301885</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2990,19 +2972,19 @@
         <x:v>2028</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>282.61182149311907</x:v>
+        <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="C4" t="n">
-        <x:v>223.73579108229808</x:v>
+        <x:v>2518.810021322432</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>447.1153396824204</x:v>
+        <x:v>4520.373753057168</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>134.53556605123794</x:v>
+        <x:v>1846.8652682262345</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>439.5107200261528</x:v>
+        <x:v>4982.8637832413215</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3010,19 +2992,19 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>317.1347022642276</x:v>
+        <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="C5" t="n">
-        <x:v>244.1199170689629</x:v>
+        <x:v>2582.6199260176004</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>552.155957512037</x:v>
+        <x:v>5096.529058813096</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>131.8018331592993</x:v>
+        <x:v>1757.8226777328273</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>536.8294461822715</x:v>
+        <x:v>5751.407153362984</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3030,13 +3012,151 @@
         <x:v>2030</x:v>
       </x:c>
       <x:c r="B6" t="n">
+        <x:v>3954.452041745783</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>2679.0610483781643</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>5725.74378702051</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>1711.7519715612111</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>6635.556261514627</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d25a21df7394b31"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>点预测</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>基准下界</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>基准上界</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>压力下界</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>压力上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>224.43130693451835</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>173.61813455540295</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>279.05169263086566</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>125.33333333333331</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>290.9090909090906</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>251.84705766167988</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>181.91455386161562</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>334.5969995162747</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>136.90256410256413</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>353.566433566433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>282.61182149311907</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>197.47747601548753</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>394.6405192534152</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>134.53556605123794</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>439.5107200261528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>317.1347022642276</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>206.68677347144515</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>467.48882549783883</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>131.8018331592993</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>536.8294461822715</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
         <x:v>355.8747785172497</x:v>
       </x:c>
       <x:c r="C6" t="n">
-        <x:v>269.9853648717954</x:v>
+        <x:v>219.26891259334394</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>677.8389767662317</x:v>
+        <x:v>550.5076744418875</x:v>
       </x:c>
       <x:c r="E6" t="n">
         <x:v>130.5555555555556</x:v>
@@ -3047,6 +3167,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R822164c72db8468c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re276d38be99e4c91"/>
 </x:worksheet>
 </file>
--- a/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
+++ b/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
@@ -2,15 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="Rafba1ea1172f4742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R828e1e47371b44d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="Rf060d033ab8b4cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="Rbabe3e8423fd40c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="Rc3df9c2420774152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="R0a703cd380f64823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R00d98201f98e425c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="8" r:id="Rcfe3092ac7f547a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="9" r:id="R0317d9d6495d4e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="Rab3b2393ecd34075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R178839b4db384e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="Rda6cc63587c2447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="Re6c1f806d31149bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="R1aa3c5f275474715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="R0d3798a3a3044135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R200ff47a705249a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性检验" sheetId="8" r:id="R98d117648fe64bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARIMA阶数比较" sheetId="9" r:id="R756a7f4348964b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="10" r:id="R3b07885f8b524e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="11" r:id="R69620e713ab14354"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0.00"/>
     <x:numFmt numFmtId="201" formatCode="0.00%"/>
     <x:numFmt numFmtId="202" formatCode="0.000000"/>
+    <x:numFmt numFmtId="203" formatCode="0.0000"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -67,7 +70,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -82,6 +85,7 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -605,7 +609,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf43eb5999104e7c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdd91ec9033a43af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -640,7 +644,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R178afdc091d14d98"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a4c6c894363478a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -651,7 +655,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{7879DC63-B7A0-4CD9-9467-94FD332062FF}"/>
+  <xltc:person displayName="User" id="{3A2A2BCD-CC9D-4F48-BF81-B8BFE5DD3DD9}"/>
 </xltc:personList>
 </file>
 
@@ -880,62 +884,354 @@
     </x:row>
     <x:row r="4" ht="21" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>2025游客量准留出</x:v>
+        <x:v>平稳性检验</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>预测2866.56，补充值2691，APE=6.52%</x:v>
+        <x:v>已补充ADF与KPSS；原对数和一阶差分结果见“平稳性检验”</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>2025旅游收入准留出</x:v>
+        <x:v>阶数比较</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>预测251.84，补充值200，APE=25.92%</x:v>
+        <x:v>已比较p,q=0—2的9种ARIMA(p,1,q)，见“ARIMA阶数比较”</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>2030基准预测</x:v>
+        <x:v>2025游客量准留出</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>游客量3954.45万人次；旅游收入355.87亿元</x:v>
+        <x:v>预测2866.56，补充值2691，APE=6.52%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="21" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>区间设计</x:v>
+        <x:v>2025旅游收入准留出</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>基准区间排除2020极端残差后重新中心化；压力区间保留全部残差并中心化</x:v>
+        <x:v>预测251.84，补充值200，APE=25.92%</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="21" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>敏感性</x:v>
+        <x:v>2030基准预测</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>插补不改变点预测，但会改变Bootstrap区间</x:v>
+        <x:v>游客量3954.45万人次；旅游收入355.87亿元</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="21" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>COVID解释</x:v>
+        <x:v>区间设计</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>系数表示年度增长率影响；水平损失使用反事实路径另算</x:v>
+        <x:v>基准区间排除2020极端残差后重新中心化；压力区间保留全部残差并中心化</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="21" customHeight="1">
       <x:c r="A10" s="5" t="str">
+        <x:v>敏感性</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>插补不改变点预测，但会改变Bootstrap区间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>COVID解释</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>系数表示年度增长率影响；水平损失使用反事实路径另算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" s="5" t="str">
         <x:v>使用限制</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="B12" s="6" t="str">
         <x:v>年度小样本；2025旅游值不是严格政府统计实测；远期区间较宽</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>点预测</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>基准下界</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>基准上界</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>压力下界</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>压力上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>2906.3520568538356</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>2401.8353068406677</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>3366.4764259197964</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>1781.5669392857153</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>3486.241273584903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>3138.93804473375</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>2432.0597844187496</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>3900.9911145776214</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>1868.164130763831</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>4183.489528301885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>3390.13713959446</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>2518.810021322432</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>4520.373753057168</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>1846.8652682262345</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>4982.8637832413215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>3661.438888397227</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>2582.6199260176004</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>5096.529058813096</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>1757.8226777328273</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>5751.407153362984</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>3954.452041745783</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>2679.0610483781643</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>5725.74378702051</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>1711.7519715612111</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>6635.556261514627</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R945628cc6f9a47d6"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>点预测</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>基准下界</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>基准上界</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>压力下界</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>压力上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>224.43130693451835</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>173.61813455540295</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>279.05169263086566</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>125.33333333333331</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>290.9090909090906</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>251.84705766167988</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>181.91455386161562</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>334.5969995162747</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>136.90256410256413</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>353.566433566433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>282.61182149311907</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>197.47747601548753</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>394.6405192534152</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>134.53556605123794</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>439.5107200261528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>317.1347022642276</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>206.68677347144515</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>467.48882549783883</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>131.8018331592993</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>536.8294461822715</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
+        <x:v>355.8747785172497</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>219.26891259334394</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>550.5076744418875</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>130.5555555555556</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>652.7380311995681</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R300024fbb9af41e9"/>
 </x:worksheet>
 </file>
 
@@ -2899,137 +3195,308 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="31" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="31" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>年份</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>点预测</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>基准下界</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>基准上界</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>压力下界</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>压力上界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="B2" t="n">
-        <x:v>2906.3520568538356</x:v>
-      </x:c>
-      <x:c r="C2" t="n">
-        <x:v>2401.8353068406677</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
-        <x:v>3366.4764259197964</x:v>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>regression</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>ADF_stat</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>ADF_lag_BIC</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>ADF_nobs</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>ADF_crit_1pct</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>ADF_crit_5pct</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str">
+        <x:v>ADF_crit_10pct</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="str">
+        <x:v>ADF_conclusion_5pct</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="str">
+        <x:v>KPSS_stat</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>KPSS_lag</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>KPSS_nobs</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>KPSS_crit_1pct</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>KPSS_crit_5pct</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>KPSS_crit_10pct</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>KPSS_conclusion_5pct</x:v>
+      </x:c>
+      <x:c r="R1" s="3" t="str">
+        <x:v>joint_conclusion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>ct</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="n">
+        <x:v>-1.8645905952222277</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>1781.5669392857153</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>3486.241273584903</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>2027</x:v>
-      </x:c>
-      <x:c r="B3" t="n">
-        <x:v>3138.93804473375</x:v>
-      </x:c>
-      <x:c r="C3" t="n">
-        <x:v>2432.0597844187496</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>3900.9911145776214</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="n">
+        <x:v>-4.7284062962962965</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="n">
+        <x:v>-3.7567874814814814</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="n">
+        <x:v>-3.323498888888889</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>不能拒绝单位根，序列非平稳</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="n">
+        <x:v>0.13591119875416943</x:v>
+      </x:c>
+      <x:c r="L2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N2" s="10" t="n">
+        <x:v>0.216</x:v>
+      </x:c>
+      <x:c r="O2" s="10" t="n">
+        <x:v>0.146</x:v>
+      </x:c>
+      <x:c r="P2" s="10" t="n">
+        <x:v>0.119</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>不能拒绝平稳性，序列平稳</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>结论不完全一致，结合图形与差分结果判断</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="n">
+        <x:v>-2.9430265625938654</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>1868.164130763831</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>4183.489528301885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>2028</x:v>
-      </x:c>
-      <x:c r="B4" t="n">
-        <x:v>3390.13713959446</x:v>
-      </x:c>
-      <x:c r="C4" t="n">
-        <x:v>2518.810021322432</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>4520.373753057168</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="n">
+        <x:v>-4.0120336005830906</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="n">
+        <x:v>-3.1041838775510207</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="n">
+        <x:v>-2.6922555685131195</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>不能拒绝单位根，序列非平稳</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="n">
+        <x:v>0.21281563795210665</x:v>
+      </x:c>
+      <x:c r="L3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N3" s="10" t="n">
+        <x:v>0.739</x:v>
+      </x:c>
+      <x:c r="O3" s="10" t="n">
+        <x:v>0.463</x:v>
+      </x:c>
+      <x:c r="P3" s="10" t="n">
+        <x:v>0.347</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>不能拒绝平稳性，序列平稳</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v>结论不完全一致，结合图形与差分结果判断</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>ct</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="n">
+        <x:v>-2.0380783074966087</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>1846.8652682262345</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>4982.8637832413215</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>2029</x:v>
-      </x:c>
-      <x:c r="B5" t="n">
-        <x:v>3661.438888397227</x:v>
-      </x:c>
-      <x:c r="C5" t="n">
-        <x:v>2582.6199260176004</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>5096.529058813096</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="n">
+        <x:v>-4.7284062962962965</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="n">
+        <x:v>-3.7567874814814814</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="n">
+        <x:v>-3.323498888888889</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>不能拒绝单位根，序列非平稳</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="n">
+        <x:v>0.1252292954790474</x:v>
+      </x:c>
+      <x:c r="L4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N4" s="10" t="n">
+        <x:v>0.216</x:v>
+      </x:c>
+      <x:c r="O4" s="10" t="n">
+        <x:v>0.146</x:v>
+      </x:c>
+      <x:c r="P4" s="10" t="n">
+        <x:v>0.119</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>不能拒绝平稳性，序列平稳</x:v>
+      </x:c>
+      <x:c r="R4" t="str">
+        <x:v>结论不完全一致，结合图形与差分结果判断</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="n">
+        <x:v>-3.1510201253768795</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>1757.8226777328273</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>5751.407153362984</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>2030</x:v>
-      </x:c>
-      <x:c r="B6" t="n">
-        <x:v>3954.452041745783</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>2679.0610483781643</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>5725.74378702051</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>1711.7519715612111</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>6635.556261514627</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="n">
+        <x:v>-4.0120336005830906</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="n">
+        <x:v>-3.1041838775510207</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="n">
+        <x:v>-2.6922555685131195</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>拒绝单位根，序列平稳</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="n">
+        <x:v>0.19881885409174818</x:v>
+      </x:c>
+      <x:c r="L5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N5" s="10" t="n">
+        <x:v>0.739</x:v>
+      </x:c>
+      <x:c r="O5" s="10" t="n">
+        <x:v>0.463</x:v>
+      </x:c>
+      <x:c r="P5" s="10" t="n">
+        <x:v>0.347</x:v>
+      </x:c>
+      <x:c r="Q5" t="str">
+        <x:v>不能拒绝平稳性，序列平稳</x:v>
+      </x:c>
+      <x:c r="R5" t="str">
+        <x:v>支持平稳</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d25a21df7394b31"/>
 </x:worksheet>
 </file>
 
@@ -3037,136 +3504,1009 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="19" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>年份</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>点预测</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>基准下界</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>基准上界</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>压力下界</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>压力上界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>2026</x:v>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>p</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>d</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>q</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>parameter_count_including_variance</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>conditional_loglik</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>AIC</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>AICc</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str">
+        <x:v>BIC</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="str">
+        <x:v>in_sample_RMSE_dlog</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="str">
+        <x:v>rolling_MAPE_2023_2025_pct</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>drift_mean_dlog</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>AR_parameters</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>MA_parameters</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>parameter_boundary_flag</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>selected_main_model</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>selection_note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>224.43130693451835</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>173.61813455540295</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>279.05169263086566</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>125.33333333333331</x:v>
-      </x:c>
-      <x:c r="F2" t="n">
-        <x:v>290.9090909090906</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>2027</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="n">
+        <x:v>6.669366580401672</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="n">
+        <x:v>-9.338733160803343</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="n">
+        <x:v>-8.338733160803343</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="n">
+        <x:v>-7.922632758598923</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="n">
+        <x:v>0.1551189601022152</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="n">
+        <x:v>3.581861766943781</x:v>
+      </x:c>
+      <x:c r="L2" s="10" t="n">
+        <x:v>0.07698583432900019</x:v>
+      </x:c>
+      <x:c r="M2" t="str"/>
+      <x:c r="N2" t="str"/>
+      <x:c r="O2" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>主模型：结构最简，且滚动预测稳定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>251.84705766167988</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>181.91455386161562</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>334.5969995162747</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>136.90256410256413</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>353.566433566433</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>2028</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="n">
+        <x:v>7.25583938945928</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="n">
+        <x:v>-8.51167877891856</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="n">
+        <x:v>-6.329860597100378</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="n">
+        <x:v>-6.38752817561193</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="n">
+        <x:v>0.14917112245591646</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="n">
+        <x:v>8.505295141202156</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="n">
+        <x:v>0.08245363187251606</x:v>
+      </x:c>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="n">
+        <x:v>0.374837</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>282.61182149311907</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" t="n">
-        <x:v>197.47747601548753</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>394.6405192534152</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>134.53556605123794</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>439.5107200261528</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>2029</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="n">
+        <x:v>7.633539964673126</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="n">
+        <x:v>-7.267079929346252</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="n">
+        <x:v>-3.2670799293462522</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="n">
+        <x:v>-4.434879124937412</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="n">
+        <x:v>0.14546188324492265</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="n">
+        <x:v>6.473547757057769</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="n">
+        <x:v>0.07856079837411425</x:v>
+      </x:c>
+      <x:c r="M4" t="str"/>
+      <x:c r="N4" t="str">
+        <x:v>0.288220;-0.244209</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>317.1347022642276</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="n">
-        <x:v>206.68677347144515</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>467.48882549783883</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>131.8018331592993</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>536.8294461822715</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>2030</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="n">
+        <x:v>6.994258289440421</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="n">
+        <x:v>-7.9885165788808425</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="n">
+        <x:v>-5.806698397062661</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="n">
+        <x:v>-5.864365975574213</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="n">
+        <x:v>0.1517952934916852</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="n">
+        <x:v>5.674847008275485</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="n">
+        <x:v>0.07985582939254779</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>0.207792</x:v>
+      </x:c>
+      <x:c r="N5" t="str"/>
+      <x:c r="O5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q5" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>355.8747785172497</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="n">
-        <x:v>219.26891259334394</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>550.5076744418875</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>130.5555555555556</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>652.7380311995681</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>7.547739457627518</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="n">
+        <x:v>-7.095478915255036</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="n">
+        <x:v>-3.095478915255036</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="n">
+        <x:v>-4.263278110846196</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="n">
+        <x:v>0.14629631434606008</x:v>
+      </x:c>
+      <x:c r="K6" s="10" t="n">
+        <x:v>6.458903040974937</x:v>
+      </x:c>
+      <x:c r="L6" s="10" t="n">
+        <x:v>0.08149132663248473</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>-0.386742</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0.718762</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q6" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="n">
+        <x:v>13.372793746834459</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="n">
+        <x:v>-16.745587493668918</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="n">
+        <x:v>-10.07892082700225</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="n">
+        <x:v>-13.205336488157867</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="n">
+        <x:v>0.09921578877408797</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="n">
+        <x:v>10.563787306196321</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="n">
+        <x:v>0.15893320773561326</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0.642182</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>-0.980000;-0.980000</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q7" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>7.4487109459176795</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="n">
+        <x:v>-6.897421891835359</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="n">
+        <x:v>-2.897421891835359</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="n">
+        <x:v>-4.065221087426519</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="n">
+        <x:v>0.14726534329483623</x:v>
+      </x:c>
+      <x:c r="K8" s="10" t="n">
+        <x:v>10.52670979670538</x:v>
+      </x:c>
+      <x:c r="L8" s="10" t="n">
+        <x:v>0.07783360228603195</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>0.258702;-0.244699</x:v>
+      </x:c>
+      <x:c r="N8" t="str"/>
+      <x:c r="O8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P8" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q8" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>7.596876498966699</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="n">
+        <x:v>-5.193752997933398</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="n">
+        <x:v>1.472913668733269</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="n">
+        <x:v>-1.6535019924223473</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="n">
+        <x:v>0.14581786056430165</x:v>
+      </x:c>
+      <x:c r="K9" s="10" t="n">
+        <x:v>15.637529459830638</x:v>
+      </x:c>
+      <x:c r="L9" s="10" t="n">
+        <x:v>0.07998350750520511</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>-0.330656;-0.102823</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>0.638893</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q9" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>13.65279460003364</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="n">
+        <x:v>-15.305589200067281</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="n">
+        <x:v>-4.805589200067281</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="n">
+        <x:v>-11.057287993454022</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="n">
+        <x:v>0.09738093371838893</x:v>
+      </x:c>
+      <x:c r="K10" s="10" t="n">
+        <x:v>9.231743467832647</x:v>
+      </x:c>
+      <x:c r="L10" s="10" t="n">
+        <x:v>0.15892229633197025</x:v>
+      </x:c>
+      <x:c r="M10" t="str">
+        <x:v>0.522067;0.199826</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>-0.980000;-0.980000</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P10" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q10" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>4.084395794735093</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="n">
+        <x:v>-4.168791589470185</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="n">
+        <x:v>-3.1687915894701852</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="n">
+        <x:v>-2.752691187265765</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="n">
+        <x:v>0.1842924121785992</x:v>
+      </x:c>
+      <x:c r="K11" s="10" t="n">
+        <x:v>10.850665292333863</x:v>
+      </x:c>
+      <x:c r="L11" s="10" t="n">
+        <x:v>0.11525231133777775</x:v>
+      </x:c>
+      <x:c r="M11" t="str"/>
+      <x:c r="N11" t="str"/>
+      <x:c r="O11" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="Q11" t="str">
+        <x:v>主模型：结构最简，且滚动预测稳定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>4.133532094533928</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="n">
+        <x:v>-2.267064189067856</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="n">
+        <x:v>-0.08524600724967435</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="n">
+        <x:v>-0.14291358576122626</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="n">
+        <x:v>0.18368970339916138</x:v>
+      </x:c>
+      <x:c r="K12" s="10" t="n">
+        <x:v>9.850029698839215</x:v>
+      </x:c>
+      <x:c r="L12" s="10" t="n">
+        <x:v>0.11483380845531646</x:v>
+      </x:c>
+      <x:c r="M12" t="str"/>
+      <x:c r="N12" t="n">
+        <x:v>0.114831</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q12" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>4.743465831715998</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="n">
+        <x:v>-1.4869316634319958</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="n">
+        <x:v>2.513068336568004</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="n">
+        <x:v>1.3452691409768445</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="n">
+        <x:v>0.17637028735060822</x:v>
+      </x:c>
+      <x:c r="K13" s="10" t="n">
+        <x:v>10.803182051650802</x:v>
+      </x:c>
+      <x:c r="L13" s="10" t="n">
+        <x:v>0.11482178703026194</x:v>
+      </x:c>
+      <x:c r="M13" t="str"/>
+      <x:c r="N13" t="str">
+        <x:v>0.006337;-0.359805</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P13" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q13" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="n">
+        <x:v>4.109274658210112</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="n">
+        <x:v>-2.2185493164202246</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="n">
+        <x:v>-0.036731134602042914</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="n">
+        <x:v>-0.09439871311359482</x:v>
+      </x:c>
+      <x:c r="J14" s="10" t="n">
+        <x:v>0.18398699980823033</x:v>
+      </x:c>
+      <x:c r="K14" s="10" t="n">
+        <x:v>10.344495248838271</x:v>
+      </x:c>
+      <x:c r="L14" s="10" t="n">
+        <x:v>0.1149871350876682</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>0.060372</x:v>
+      </x:c>
+      <x:c r="N14" t="str"/>
+      <x:c r="O14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P14" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q14" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="n">
+        <x:v>4.880285295206788</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="n">
+        <x:v>-1.7605705904135753</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="n">
+        <x:v>2.2394294095864247</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="n">
+        <x:v>1.071630213995265</x:v>
+      </x:c>
+      <x:c r="J15" s="10" t="n">
+        <x:v>0.17476887605519395</x:v>
+      </x:c>
+      <x:c r="K15" s="10" t="n">
+        <x:v>10.355335461145602</x:v>
+      </x:c>
+      <x:c r="L15" s="10" t="n">
+        <x:v>0.12404013113911966</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>0.747258</x:v>
+      </x:c>
+      <x:c r="N15" t="n">
+        <x:v>-0.98</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P15" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q15" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="n">
+        <x:v>9.750349878287581</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="n">
+        <x:v>-9.500699756575163</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="n">
+        <x:v>-2.8340330899084956</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="n">
+        <x:v>-5.960448751064112</x:v>
+      </x:c>
+      <x:c r="J16" s="10" t="n">
+        <x:v>0.1263168484324846</x:v>
+      </x:c>
+      <x:c r="K16" s="10" t="n">
+        <x:v>15.3133999725367</x:v>
+      </x:c>
+      <x:c r="L16" s="10" t="n">
+        <x:v>0.19537335965568486</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>0.384329</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>-0.980000;-0.980000</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P16" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q16" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="n">
+        <x:v>4.621572645412217</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="n">
+        <x:v>-1.2431452908244331</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="n">
+        <x:v>2.756854709175567</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="n">
+        <x:v>1.589055513584407</x:v>
+      </x:c>
+      <x:c r="J17" s="10" t="n">
+        <x:v>0.177809348911137</x:v>
+      </x:c>
+      <x:c r="K17" s="10" t="n">
+        <x:v>11.7721089883981</x:v>
+      </x:c>
+      <x:c r="L17" s="10" t="n">
+        <x:v>0.115916896948102</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>0.080023;-0.270103</x:v>
+      </x:c>
+      <x:c r="N17" t="str"/>
+      <x:c r="O17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="P17" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q17" t="str">
+        <x:v>候选模型，不作为主模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="n">
+        <x:v>5.202791704799166</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="n">
+        <x:v>-0.40558340959833217</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="n">
+        <x:v>6.261083257068335</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="n">
+        <x:v>3.1346675959127186</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="n">
+        <x:v>0.17105137764804748</x:v>
+      </x:c>
+      <x:c r="K18" s="10" t="n">
+        <x:v>17.852602164465736</x:v>
+      </x:c>
+      <x:c r="L18" s="10" t="n">
+        <x:v>0.12558743463255073</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>0.906720;-0.218099</x:v>
+      </x:c>
+      <x:c r="N18" t="n">
+        <x:v>-0.98</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q18" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="n">
+        <x:v>10.293241458850947</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="n">
+        <x:v>-8.586482917701893</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="n">
+        <x:v>1.9135170822981067</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="n">
+        <x:v>-4.338181711088634</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="n">
+        <x:v>0.12182683467287349</x:v>
+      </x:c>
+      <x:c r="K19" s="10" t="n">
+        <x:v>12.93990921167224</x:v>
+      </x:c>
+      <x:c r="L19" s="10" t="n">
+        <x:v>0.19534822212900743</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>0.288258;0.287345</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>-0.980000;-0.980000</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="Q19" t="str">
+        <x:v>参数接近边界，存在小样本过拟合风险</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re276d38be99e4c91"/>
 </x:worksheet>
 </file>
--- a/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
+++ b/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
@@ -2,17 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="Rab3b2393ecd34075"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R178839b4db384e4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="Rda6cc63587c2447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="Re6c1f806d31149bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="R1aa3c5f275474715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="R0d3798a3a3044135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R200ff47a705249a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性检验" sheetId="8" r:id="R98d117648fe64bcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARIMA阶数比较" sheetId="9" r:id="R756a7f4348964b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="10" r:id="R3b07885f8b524e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="11" r:id="R69620e713ab14354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="R83aa2fd4fb3a4b6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="Rf480b11e765e453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="R3ed28677b13242bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="R1beda91cb31a4026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="Rc0f68cabe5ed4f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="Reb38931f2ea349eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R6dad44a87083446b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性检验" sheetId="8" r:id="R9f0c4962fbce4132"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARIMA阶数比较" sheetId="9" r:id="R1cc8aa46f6b94b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性数据" sheetId="10" r:id="R0f3df804586549d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACF_PACF数值" sheetId="11" r:id="R7d1141dfbd3c4d14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="12" r:id="Re2a8b5be840b475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="13" r:id="R59bd68bcb9b04e5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -609,7 +611,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdd91ec9033a43af"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdc41ef43c294531"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -644,7 +646,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a4c6c894363478a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce0e379d09484341"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -655,7 +657,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{3A2A2BCD-CC9D-4F48-BF81-B8BFE5DD3DD9}"/>
+  <xltc:person displayName="User" id="{DA81F2DD-B489-4F2C-8FFC-C0A15448CA99}"/>
 </xltc:personList>
 </file>
 
@@ -963,141 +965,933 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>年份</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>点预测</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>基准下界</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>基准上界</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>压力下界</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>压力上界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>2026</x:v>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>year</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>original_value</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>log_value</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>dlog_value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>2906.3520568538356</x:v>
-      </x:c>
-      <x:c r="C2" t="n">
-        <x:v>2401.8353068406677</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
-        <x:v>3366.4764259197964</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>1781.5669392857153</x:v>
-      </x:c>
-      <x:c r="F2" t="n">
-        <x:v>3486.241273584903</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>2027</x:v>
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="n">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>6.742880635791903</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>3138.93804473375</x:v>
-      </x:c>
-      <x:c r="C3" t="n">
-        <x:v>2432.0597844187496</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>3900.9911145776214</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>1868.164130763831</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>4183.489528301885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>2028</x:v>
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="n">
+        <x:v>1098.6</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>7.00179192090852</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>0.2589112851166169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>3390.13713959446</x:v>
-      </x:c>
-      <x:c r="C4" t="n">
-        <x:v>2518.810021322432</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>4520.373753057168</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>1846.8652682262345</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>4982.8637832413215</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>2029</x:v>
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="n">
+        <x:v>1152</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="n">
+        <x:v>7.049254841255837</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="n">
+        <x:v>0.04746292034731692</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>3661.438888397227</x:v>
-      </x:c>
-      <x:c r="C5" t="n">
-        <x:v>2582.6199260176004</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>5096.529058813096</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>1757.8226777328273</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>5751.407153362984</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>2030</x:v>
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="n">
+        <x:v>1295</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>7.166265974133638</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>0.11701113287780096</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>游客接待量_主插补</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>3954.452041745783</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>2679.0610483781643</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>5725.74378702051</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>1711.7519715612111</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>6635.556261514627</x:v>
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="n">
+        <x:v>1554</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="n">
+        <x:v>7.348587530927593</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="n">
+        <x:v>0.1823215567939549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="n">
+        <x:v>1814.4</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="n">
+        <x:v>7.503510113533433</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="n">
+        <x:v>0.15492258260584002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="n">
+        <x:v>2086.27</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="n">
+        <x:v>7.643133061508884</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="n">
+        <x:v>0.13962294797545116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="n">
+        <x:v>7.783224016336037</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="n">
+        <x:v>0.14009095482715317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="n">
+        <x:v>2660</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="n">
+        <x:v>7.886081401775745</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="n">
+        <x:v>0.1028573854397079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="n">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="n">
+        <x:v>7.937374696163295</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="n">
+        <x:v>0.05129329438755015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="n">
+        <x:v>1853.73</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="n">
+        <x:v>7.524955104452606</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="n">
+        <x:v>-0.4124195917106892</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B13" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="n">
+        <x:v>1713.3964702354788</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="n">
+        <x:v>7.446232919434136</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="n">
+        <x:v>-0.07872218501846984</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="n">
+        <x:v>2203.23434541834</x:v>
+      </x:c>
+      <x:c r="D14" s="9" t="n">
+        <x:v>7.6976817167319425</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="n">
+        <x:v>0.25144879729780634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="n">
+        <x:v>2363</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="n">
+        <x:v>7.767687277186908</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="n">
+        <x:v>0.0700055604549652</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B16" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="n">
+        <x:v>2643</x:v>
+      </x:c>
+      <x:c r="D16" s="9" t="n">
+        <x:v>7.879669914604289</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="n">
+        <x:v>0.11198263741738135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="n">
+        <x:v>2691</x:v>
+      </x:c>
+      <x:c r="D17" s="9" t="n">
+        <x:v>7.897668150726906</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="n">
+        <x:v>0.017998236122616973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="n">
+        <x:v>35.5</x:v>
+      </x:c>
+      <x:c r="D18" s="9" t="n">
+        <x:v>3.56953269648137</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="str"/>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B19" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D19" s="9" t="n">
+        <x:v>3.828641396489095</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="n">
+        <x:v>0.259108700007725</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="21" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B20" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D20" s="9" t="n">
+        <x:v>3.9512437185814275</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="n">
+        <x:v>0.12260232209233246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="21" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="n">
+        <x:v>63.2</x:v>
+      </x:c>
+      <x:c r="D21" s="9" t="n">
+        <x:v>4.146304301152812</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="n">
+        <x:v>0.19506058257138426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="21" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B22" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D22" s="9" t="n">
+        <x:v>4.3694478524670215</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="n">
+        <x:v>0.2231435513142097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="21" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D23" s="9" t="n">
+        <x:v>4.543294782270004</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="n">
+        <x:v>0.17384692980298233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="21" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B24" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="n">
+        <x:v>109.6</x:v>
+      </x:c>
+      <x:c r="D24" s="9" t="n">
+        <x:v>4.696837374513915</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="n">
+        <x:v>0.15354259224391154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="21" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="C25" s="9" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D25" s="9" t="n">
+        <x:v>4.867534450455582</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="n">
+        <x:v>0.17069707594166683</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="21" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B26" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D26" s="9" t="n">
+        <x:v>4.955827057601261</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="n">
+        <x:v>0.08829260714567866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="21" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B27" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="C27" s="9" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D27" s="9" t="n">
+        <x:v>5.10594547390058</x:v>
+      </x:c>
+      <x:c r="E27" s="9" t="n">
+        <x:v>0.15011841629931943</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="21" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="n">
+        <x:v>103.4</x:v>
+      </x:c>
+      <x:c r="D28" s="9" t="n">
+        <x:v>4.638604962074329</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="n">
+        <x:v>-0.4673405118262517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="21" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="C29" s="9" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D29" s="9" t="n">
+        <x:v>4.700480365792417</x:v>
+      </x:c>
+      <x:c r="E29" s="9" t="n">
+        <x:v>0.06187540371808797</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="21" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D30" s="9" t="n">
+        <x:v>5.075173815233827</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="n">
+        <x:v>0.37469344944141003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="21" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="C31" s="9" t="n">
+        <x:v>191.5</x:v>
+      </x:c>
+      <x:c r="D31" s="9" t="n">
+        <x:v>5.2548878086207</x:v>
+      </x:c>
+      <x:c r="E31" s="9" t="n">
+        <x:v>0.17971399338687366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="21" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="C32" s="9" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D32" s="9" t="n">
+        <x:v>5.3981627015177525</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="n">
+        <x:v>0.1432748928970522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="21" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C33" s="9" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D33" s="9" t="n">
+        <x:v>5.298317366548036</x:v>
+      </x:c>
+      <x:c r="E33" s="9" t="n">
+        <x:v>-0.09984533496971615</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R945628cc6f9a47d6"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>lag</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>ACF</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>PACF</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>CI95_upper</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>CI95_lower</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>sample_size</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>0.2043675090347722</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>0.2043675090347722</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="n">
+        <x:v>-0.18738736352966115</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="n">
+        <x:v>-0.23914144260264913</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>-0.0700842196099105</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>0.029047555053533423</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H5" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="n">
+        <x:v>-0.0780007295043552</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="n">
+        <x:v>-0.12395719090529025</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="n">
+        <x:v>-0.003423799365727777</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="n">
+        <x:v>0.038877494473560155</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="n">
+        <x:v>0.054856895274183054</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="n">
+        <x:v>0.054856895274183054</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="n">
+        <x:v>-0.23968360228486896</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="n">
+        <x:v>-0.2434254162271597</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="n">
+        <x:v>-0.18044387174376883</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="n">
+        <x:v>-0.1607199857439133</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="n">
+        <x:v>-0.044338923686842766</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="n">
+        <x:v>-0.094114625556733</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="n">
+        <x:v>0.21647333367429517</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="n">
+        <x:v>0.15293311742618618</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="n">
+        <x:v>0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="n">
+        <x:v>-0.5060698239044358</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1134,19 +1928,19 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>224.43130693451835</x:v>
+        <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>173.61813455540295</x:v>
+        <x:v>2401.8353068406677</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>279.05169263086566</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>125.33333333333331</x:v>
+        <x:v>1781.5669392857153</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>290.9090909090906</x:v>
+        <x:v>3486.241273584903</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1154,19 +1948,19 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>251.84705766167988</x:v>
+        <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>181.91455386161562</x:v>
+        <x:v>2432.0597844187496</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>334.5969995162747</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>136.90256410256413</x:v>
+        <x:v>1868.164130763831</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>353.566433566433</x:v>
+        <x:v>4183.489528301885</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1174,19 +1968,19 @@
         <x:v>2028</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>282.61182149311907</x:v>
+        <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="C4" t="n">
-        <x:v>197.47747601548753</x:v>
+        <x:v>2518.810021322432</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>394.6405192534152</x:v>
+        <x:v>4520.373753057168</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>134.53556605123794</x:v>
+        <x:v>1846.8652682262345</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>439.5107200261528</x:v>
+        <x:v>4982.8637832413215</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1194,19 +1988,19 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>317.1347022642276</x:v>
+        <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="C5" t="n">
-        <x:v>206.68677347144515</x:v>
+        <x:v>2582.6199260176004</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>467.48882549783883</x:v>
+        <x:v>5096.529058813096</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>131.8018331592993</x:v>
+        <x:v>1757.8226777328273</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>536.8294461822715</x:v>
+        <x:v>5751.407153362984</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1214,6 +2008,144 @@
         <x:v>2030</x:v>
       </x:c>
       <x:c r="B6" t="n">
+        <x:v>3954.452041745783</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>2679.0610483781643</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>5725.74378702051</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>1711.7519715612111</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>6635.556261514627</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42016fb72c424ab8"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>点预测</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>基准下界</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>基准上界</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>压力下界</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>压力上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>224.43130693451835</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>173.61813455540295</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>279.05169263086566</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>125.33333333333331</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>290.9090909090906</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>251.84705766167988</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>181.91455386161562</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>334.5969995162747</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>136.90256410256413</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>353.566433566433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>282.61182149311907</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>197.47747601548753</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>394.6405192534152</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>134.53556605123794</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>439.5107200261528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>317.1347022642276</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>206.68677347144515</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>467.48882549783883</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>131.8018331592993</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>536.8294461822715</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
         <x:v>355.8747785172497</x:v>
       </x:c>
       <x:c r="C6" t="n">
@@ -1231,7 +2163,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R300024fbb9af41e9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11026efe760148b7"/>
 </x:worksheet>
 </file>
 

--- a/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
+++ b/outputs/q2_revised/第二问_ARIMA修订建模结果.xlsx
@@ -2,19 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="R83aa2fd4fb3a4b6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="Rf480b11e765e453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="R3ed28677b13242bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="R1beda91cb31a4026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="Rc0f68cabe5ed4f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="Reb38931f2ea349eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R6dad44a87083446b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性检验" sheetId="8" r:id="R9f0c4962fbce4132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARIMA阶数比较" sheetId="9" r:id="R1cc8aa46f6b94b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性数据" sheetId="10" r:id="R0f3df804586549d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACF_PACF数值" sheetId="11" r:id="R7d1141dfbd3c4d14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="12" r:id="Re2a8b5be840b475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="13" r:id="R59bd68bcb9b04e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论说明" sheetId="1" r:id="R3af7e8c8980d4a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建模数据" sheetId="2" r:id="R9deff8db654a4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型验证" sheetId="3" r:id="R24981b167c7b4940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测结果" sheetId="4" r:id="Rdf0fddec5d8140f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="插补敏感性" sheetId="5" r:id="R27d9cb5fcc79415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COVID反事实" sheetId="6" r:id="Rf5ca201f1ef94cf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap审计" sheetId="7" r:id="R1ed3b5e3f342481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性检验" sheetId="8" r:id="R7e398597a54a4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARIMA阶数比较" sheetId="9" r:id="R29e807f2638a4dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平稳性数据" sheetId="10" r:id="R3696c7ce5d2a45a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACF_PACF数值" sheetId="11" r:id="Rf9320258ef35470b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hurst结果" sheetId="12" r:id="R4f5b8f69fa4d45f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hurst尺度数据" sheetId="13" r:id="R6c2720b99b334fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_游客量" sheetId="14" r:id="Rf177db0576d84259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图_旅游收入" sheetId="15" r:id="R415619c37f414520"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -611,7 +613,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdc41ef43c294531"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R54a63b40c79a4aa0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -646,7 +648,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rce0e379d09484341"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d496a4bb98442bc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -657,7 +659,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="User" id="{DA81F2DD-B489-4F2C-8FFC-C0A15448CA99}"/>
+  <xltc:person displayName="User" id="{94DFA273-12AC-45FF-9971-283E0B61A602}"/>
 </xltc:personList>
 </file>
 
@@ -1895,141 +1897,1497 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>年份</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>点预测</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>基准下界</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>基准上界</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>压力下界</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>压力上界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="B2" t="n">
-        <x:v>2906.3520568538356</x:v>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>sample_size</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>Hurst_H</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>intercept</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>R_squared</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>interpretation</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>usage_note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>原对数</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>2401.8353068406677</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
-        <x:v>3366.4764259197964</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>1781.5669392857153</x:v>
-      </x:c>
-      <x:c r="F2" t="n">
-        <x:v>3486.241273584903</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="n">
-        <x:v>2027</x:v>
-      </x:c>
-      <x:c r="B3" t="n">
-        <x:v>3138.93804473375</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
+        <x:v>0.9426245588845541</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>-0.8475080273411753</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>0.9812817069453296</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>持续性</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>探索性辅助，不用于直接决定ARIMA阶数或增长率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>对数一阶差分</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>2432.0597844187496</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>3900.9911145776214</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>1868.164130763831</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
-        <x:v>4183.489528301885</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="n">
-        <x:v>2028</x:v>
-      </x:c>
-      <x:c r="B4" t="n">
-        <x:v>3390.13713959446</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
+        <x:v>0.8092778616127345</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>-0.717132051723806</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>0.994104779686428</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>持续性</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>探索性辅助，不用于直接决定ARIMA阶数或增长率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>原对数</x:v>
       </x:c>
       <x:c r="C4" t="n">
-        <x:v>2518.810021322432</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>4520.373753057168</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>1846.8652682262345</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>4982.8637832413215</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="n">
-        <x:v>2029</x:v>
-      </x:c>
-      <x:c r="B5" t="n">
-        <x:v>3661.438888397227</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="n">
+        <x:v>0.9920888969700165</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="n">
+        <x:v>-0.9486534677670357</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="n">
+        <x:v>0.9944917315917701</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>持续性</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>探索性辅助，不用于直接决定ARIMA阶数或增长率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>对数一阶差分</x:v>
       </x:c>
       <x:c r="C5" t="n">
-        <x:v>2582.6199260176004</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>5096.529058813096</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>1757.8226777328273</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>5751.407153362984</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="n">
-        <x:v>2030</x:v>
-      </x:c>
-      <x:c r="B6" t="n">
-        <x:v>3954.452041745783</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>2679.0610483781643</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>5725.74378702051</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>1711.7519715612111</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>6635.556261514627</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
+        <x:v>0.6758619044099476</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>-0.5527851101566202</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>0.9913141792274907</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>持续性</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>探索性辅助，不用于直接决定ARIMA阶数或增长率</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42016fb72c424ab8"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>indicator</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>scale</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>window_count</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>mean_RS</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>log_scale</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>log_RS</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>fitted_log_RS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="n">
+        <x:v>1.5362217296023624</x:v>
+      </x:c>
+      <x:c r="F2" s="9" t="n">
+        <x:v>1.3862943611198906</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="n">
+        <x:v>0.4293259795171411</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="n">
+        <x:v>0.4592470832936064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="n">
+        <x:v>1.9492569903076697</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="n">
+        <x:v>1.6094379124341003</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="n">
+        <x:v>0.6674482693535955</x:v>
+      </x:c>
+      <x:c r="H3" s="9" t="n">
+        <x:v>0.6695876749190961</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="n">
+        <x:v>2.413737129406532</x:v>
+      </x:c>
+      <x:c r="F4" s="9" t="n">
+        <x:v>1.791759469228055</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="n">
+        <x:v>0.8811762225481449</x:v>
+      </x:c>
+      <x:c r="H4" s="9" t="n">
+        <x:v>0.8414484519671428</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="n">
+        <x:v>2.8305981019158155</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="n">
+        <x:v>1.9459101490553132</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="n">
+        <x:v>1.0404880327584194</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="n">
+        <x:v>0.9867546685410662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="n">
+        <x:v>3.1983450481301525</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="n">
+        <x:v>2.0794415416798357</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="n">
+        <x:v>1.1626335035665505</x:v>
+      </x:c>
+      <x:c r="H6" s="9" t="n">
+        <x:v>1.112624638610997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="n">
+        <x:v>3.4723682818875137</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="n">
+        <x:v>2.1972245773362196</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="n">
+        <x:v>1.2448368631450801</x:v>
+      </x:c>
+      <x:c r="H7" s="9" t="n">
+        <x:v>1.2236498206406796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="n">
+        <x:v>3.609789953467643</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="n">
+        <x:v>2.302585092994046</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="n">
+        <x:v>1.283649586016996</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="n">
+        <x:v>1.3229652302364874</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="n">
+        <x:v>3.684683331803957</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="n">
+        <x:v>2.3978952727983707</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="n">
+        <x:v>1.304184587567171</x:v>
+      </x:c>
+      <x:c r="H9" s="9" t="n">
+        <x:v>1.4128069464317463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="n">
+        <x:v>4.056484545138572</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="n">
+        <x:v>2.4849066497880004</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="n">
+        <x:v>1.4003167229452127</x:v>
+      </x:c>
+      <x:c r="H10" s="9" t="n">
+        <x:v>1.4948260072845339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="n">
+        <x:v>4.675790022380267</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="n">
+        <x:v>2.5649493574615367</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="n">
+        <x:v>1.5423981372081028</x:v>
+      </x:c>
+      <x:c r="H11" s="9" t="n">
+        <x:v>1.570276229297226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="n">
+        <x:v>5.258288616527133</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="n">
+        <x:v>2.6390573296152584</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="n">
+        <x:v>1.6598056157345071</x:v>
+      </x:c>
+      <x:c r="H12" s="9" t="n">
+        <x:v>1.6401322238584568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="n">
+        <x:v>5.787066389608024</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="n">
+        <x:v>2.70805020110221</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="n">
+        <x:v>1.7556254947235852</x:v>
+      </x:c>
+      <x:c r="H13" s="9" t="n">
+        <x:v>1.7051665989100233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="n">
+        <x:v>6.256361291879173</x:v>
+      </x:c>
+      <x:c r="F14" s="9" t="n">
+        <x:v>2.772588722239781</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="n">
+        <x:v>1.833598752834929</x:v>
+      </x:c>
+      <x:c r="H14" s="9" t="n">
+        <x:v>1.766002193928388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="n">
+        <x:v>1.435002852259984</x:v>
+      </x:c>
+      <x:c r="F15" s="9" t="n">
+        <x:v>1.3862943611198906</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="n">
+        <x:v>0.3611668368472286</x:v>
+      </x:c>
+      <x:c r="H15" s="9" t="n">
+        <x:v>0.404765284409091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="n">
+        <x:v>1.8053968986556777</x:v>
+      </x:c>
+      <x:c r="F16" s="9" t="n">
+        <x:v>1.6094379124341003</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="n">
+        <x:v>0.5907804560648209</x:v>
+      </x:c>
+      <x:c r="H16" s="9" t="n">
+        <x:v>0.5853504204493261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="n">
+        <x:v>2.1182310960301445</x:v>
+      </x:c>
+      <x:c r="F17" s="9" t="n">
+        <x:v>1.791759469228055</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="n">
+        <x:v>0.7505813517229164</x:v>
+      </x:c>
+      <x:c r="H17" s="9" t="n">
+        <x:v>0.7328992200574425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="n">
+        <x:v>2.423065819782051</x:v>
+      </x:c>
+      <x:c r="F18" s="9" t="n">
+        <x:v>1.9459101490553132</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="n">
+        <x:v>0.8850336060473823</x:v>
+      </x:c>
+      <x:c r="H18" s="9" t="n">
+        <x:v>0.8576499525941954</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="n">
+        <x:v>2.6626918481935444</x:v>
+      </x:c>
+      <x:c r="F19" s="9" t="n">
+        <x:v>2.0794415416798357</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="n">
+        <x:v>0.9793375840992063</x:v>
+      </x:c>
+      <x:c r="H19" s="9" t="n">
+        <x:v>0.9657139524755394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="21" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="n">
+        <x:v>2.817303986034971</x:v>
+      </x:c>
+      <x:c r="F20" s="9" t="n">
+        <x:v>2.1972245773362196</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="n">
+        <x:v>1.0357803943377542</x:v>
+      </x:c>
+      <x:c r="H20" s="9" t="n">
+        <x:v>1.0610331557057942</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="21" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="n">
+        <x:v>3.195496918324132</x:v>
+      </x:c>
+      <x:c r="F21" s="9" t="n">
+        <x:v>2.302585092994046</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="n">
+        <x:v>1.1617426057278666</x:v>
+      </x:c>
+      <x:c r="H21" s="9" t="n">
+        <x:v>1.1462990885157749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="21" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="n">
+        <x:v>3.4993032919214477</x:v>
+      </x:c>
+      <x:c r="F22" s="9" t="n">
+        <x:v>2.3978952727983707</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="n">
+        <x:v>1.2525638892293909</x:v>
+      </x:c>
+      <x:c r="H22" s="9" t="n">
+        <x:v>1.2234315070177442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="21" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="n">
+        <x:v>3.721134111546432</x:v>
+      </x:c>
+      <x:c r="F23" s="9" t="n">
+        <x:v>2.4849066497880004</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="n">
+        <x:v>1.314028490517315</x:v>
+      </x:c>
+      <x:c r="H23" s="9" t="n">
+        <x:v>1.2938478881238913</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="21" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="n">
+        <x:v>3.9005873788469145</x:v>
+      </x:c>
+      <x:c r="F24" s="9" t="n">
+        <x:v>2.5649493574615367</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="n">
+        <x:v>1.3611271517558066</x:v>
+      </x:c>
+      <x:c r="H24" s="9" t="n">
+        <x:v>1.3586246794276238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="21" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="n">
+        <x:v>4.0580932380596675</x:v>
+      </x:c>
+      <x:c r="F25" s="9" t="n">
+        <x:v>2.6390573296152584</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="n">
+        <x:v>1.4007132174974004</x:v>
+      </x:c>
+      <x:c r="H25" s="9" t="n">
+        <x:v>1.4185986206606436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="21" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>游客接待量_主插补</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="n">
+        <x:v>4.177826811366856</x:v>
+      </x:c>
+      <x:c r="F26" s="9" t="n">
+        <x:v>2.70805020110221</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="n">
+        <x:v>1.4297912097540975</x:v>
+      </x:c>
+      <x:c r="H26" s="9" t="n">
+        <x:v>1.4744330241641261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="21" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E27" s="9" t="n">
+        <x:v>1.535804024308065</x:v>
+      </x:c>
+      <x:c r="F27" s="9" t="n">
+        <x:v>1.3862943611198906</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="n">
+        <x:v>0.42905403824429217</x:v>
+      </x:c>
+      <x:c r="H27" s="9" t="n">
+        <x:v>0.42667377583215016</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="21" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="n">
+        <x:v>1.9672575634691232</x:v>
+      </x:c>
+      <x:c r="F28" s="9" t="n">
+        <x:v>1.6094379124341003</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="n">
+        <x:v>0.6766404731169479</x:v>
+      </x:c>
+      <x:c r="H28" s="9" t="n">
+        <x:v>0.6480520155214367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="21" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E29" s="9" t="n">
+        <x:v>2.4064108618787254</x:v>
+      </x:c>
+      <x:c r="F29" s="9" t="n">
+        <x:v>1.791759469228055</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="n">
+        <x:v>0.8781363685093426</x:v>
+      </x:c>
+      <x:c r="H29" s="9" t="n">
+        <x:v>0.8289312076950075</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="21" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="n">
+        <x:v>2.666855696341898</x:v>
+      </x:c>
+      <x:c r="F30" s="9" t="n">
+        <x:v>1.9459101490553132</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="n">
+        <x:v>0.9809001366276351</x:v>
+      </x:c>
+      <x:c r="H30" s="9" t="n">
+        <x:v>0.9818623856120103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="21" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E31" s="9" t="n">
+        <x:v>2.911596427952625</x:v>
+      </x:c>
+      <x:c r="F31" s="9" t="n">
+        <x:v>2.0794415416798357</x:v>
+      </x:c>
+      <x:c r="G31" s="9" t="n">
+        <x:v>1.0687015314280717</x:v>
+      </x:c>
+      <x:c r="H31" s="9" t="n">
+        <x:v>1.1143373976317432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="21" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="n">
+        <x:v>3.2514871206928597</x:v>
+      </x:c>
+      <x:c r="F32" s="9" t="n">
+        <x:v>2.1972245773362196</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="n">
+        <x:v>1.1791124672836593</x:v>
+      </x:c>
+      <x:c r="H32" s="9" t="n">
+        <x:v>1.231188639557865</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="21" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E33" s="9" t="n">
+        <x:v>3.691932733794006</x:v>
+      </x:c>
+      <x:c r="F33" s="9" t="n">
+        <x:v>2.302585092994046</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="n">
+        <x:v>1.3061500970255522</x:v>
+      </x:c>
+      <x:c r="H33" s="9" t="n">
+        <x:v>1.33571563732103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="21" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="n">
+        <x:v>4.101101956088185</x:v>
+      </x:c>
+      <x:c r="F34" s="9" t="n">
+        <x:v>2.3978952727983707</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="n">
+        <x:v>1.4112557073757421</x:v>
+      </x:c>
+      <x:c r="H34" s="9" t="n">
+        <x:v>1.4302718084731165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="21" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E35" s="9" t="n">
+        <x:v>4.506146029135822</x:v>
+      </x:c>
+      <x:c r="F35" s="9" t="n">
+        <x:v>2.4849066497880004</x:v>
+      </x:c>
+      <x:c r="G35" s="9" t="n">
+        <x:v>1.5054422491937274</x:v>
+      </x:c>
+      <x:c r="H35" s="9" t="n">
+        <x:v>1.5165948294946003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="21" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E36" s="9" t="n">
+        <x:v>4.891156402609857</x:v>
+      </x:c>
+      <x:c r="F36" s="9" t="n">
+        <x:v>2.5649493574615367</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="n">
+        <x:v>1.587428758680348</x:v>
+      </x:c>
+      <x:c r="H36" s="9" t="n">
+        <x:v>1.5960043110609325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="21" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E37" s="9" t="n">
+        <x:v>5.375117994145842</x:v>
+      </x:c>
+      <x:c r="F37" s="9" t="n">
+        <x:v>2.6390573296152584</x:v>
+      </x:c>
+      <x:c r="G37" s="9" t="n">
+        <x:v>1.6817805261720025</x:v>
+      </x:c>
+      <x:c r="H37" s="9" t="n">
+        <x:v>1.669526007411603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="21" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="n">
+        <x:v>5.860230578965512</x:v>
+      </x:c>
+      <x:c r="F38" s="9" t="n">
+        <x:v>2.70805020110221</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="n">
+        <x:v>1.7681889507611441</x:v>
+      </x:c>
+      <x:c r="H38" s="9" t="n">
+        <x:v>1.737973069183887</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="21" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>原对数</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E39" s="9" t="n">
+        <x:v>6.336590196082774</x:v>
+      </x:c>
+      <x:c r="F39" s="9" t="n">
+        <x:v>2.772588722239781</x:v>
+      </x:c>
+      <x:c r="G39" s="9" t="n">
+        <x:v>1.8463407998082433</x:v>
+      </x:c>
+      <x:c r="H39" s="9" t="n">
+        <x:v>1.802001019431336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="21" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="n">
+        <x:v>1.4335147552250938</x:v>
+      </x:c>
+      <x:c r="F40" s="9" t="n">
+        <x:v>1.3862943611198906</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="n">
+        <x:v>0.3601292994345246</x:v>
+      </x:c>
+      <x:c r="H40" s="9" t="n">
+        <x:v>0.3841584368226407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="21" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E41" s="9" t="n">
+        <x:v>1.6967924517053523</x:v>
+      </x:c>
+      <x:c r="F41" s="9" t="n">
+        <x:v>1.6094379124341003</x:v>
+      </x:c>
+      <x:c r="G41" s="9" t="n">
+        <x:v>0.528739675711383</x:v>
+      </x:c>
+      <x:c r="H41" s="9" t="n">
+        <x:v>0.5349726623706613</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="21" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="n">
+        <x:v>1.932665216669181</x:v>
+      </x:c>
+      <x:c r="F42" s="9" t="n">
+        <x:v>1.791759469228055</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="n">
+        <x:v>0.6588999915736636</x:v>
+      </x:c>
+      <x:c r="H42" s="9" t="n">
+        <x:v>0.6581968569604099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="21" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C43" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E43" s="9" t="n">
+        <x:v>2.159053422187464</x:v>
+      </x:c>
+      <x:c r="F43" s="9" t="n">
+        <x:v>1.9459101490553132</x:v>
+      </x:c>
+      <x:c r="G43" s="9" t="n">
+        <x:v>0.7696698951762725</x:v>
+      </x:c>
+      <x:c r="H43" s="9" t="n">
+        <x:v>0.7623814289945489</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="21" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C44" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="n">
+        <x:v>2.3824493400143916</x:v>
+      </x:c>
+      <x:c r="F44" s="9" t="n">
+        <x:v>2.0794415416798357</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="n">
+        <x:v>0.8681290929473882</x:v>
+      </x:c>
+      <x:c r="H44" s="9" t="n">
+        <x:v>0.852630210312271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="21" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C45" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E45" s="9" t="n">
+        <x:v>2.54555930934708</x:v>
+      </x:c>
+      <x:c r="F45" s="9" t="n">
+        <x:v>2.1972245773362196</x:v>
+      </x:c>
+      <x:c r="G45" s="9" t="n">
+        <x:v>0.9343503937733929</x:v>
+      </x:c>
+      <x:c r="H45" s="9" t="n">
+        <x:v>0.9322352770981793</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="21" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="n">
+        <x:v>2.778845299670776</x:v>
+      </x:c>
+      <x:c r="F46" s="9" t="n">
+        <x:v>2.302585092994046</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="n">
+        <x:v>1.0220354815861012</x:v>
+      </x:c>
+      <x:c r="H46" s="9" t="n">
+        <x:v>1.0034444358602919</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="21" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C47" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E47" s="9" t="n">
+        <x:v>2.9771893363394915</x:v>
+      </x:c>
+      <x:c r="F47" s="9" t="n">
+        <x:v>2.3978952727983707</x:v>
+      </x:c>
+      <x:c r="G47" s="9" t="n">
+        <x:v>1.090979679722211</x:v>
+      </x:c>
+      <x:c r="H47" s="9" t="n">
+        <x:v>1.0678609554924976</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="21" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C48" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D48" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E48" s="9" t="n">
+        <x:v>3.1494107804934672</x:v>
+      </x:c>
+      <x:c r="F48" s="9" t="n">
+        <x:v>2.4849066497880004</x:v>
+      </x:c>
+      <x:c r="G48" s="9" t="n">
+        <x:v>1.1472153815291979</x:v>
+      </x:c>
+      <x:c r="H48" s="9" t="n">
+        <x:v>1.1266686304500406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="21" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C49" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E49" s="9" t="n">
+        <x:v>3.310300979638351</x:v>
+      </x:c>
+      <x:c r="F49" s="9" t="n">
+        <x:v>2.5649493574615367</x:v>
+      </x:c>
+      <x:c r="G49" s="9" t="n">
+        <x:v>1.1970391156593887</x:v>
+      </x:c>
+      <x:c r="H49" s="9" t="n">
+        <x:v>1.1807664472924055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="21" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C50" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D50" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E50" s="9" t="n">
+        <x:v>3.4223674637917236</x:v>
+      </x:c>
+      <x:c r="F50" s="9" t="n">
+        <x:v>2.6390573296152584</x:v>
+      </x:c>
+      <x:c r="G50" s="9" t="n">
+        <x:v>1.2303325524610884</x:v>
+      </x:c>
+      <x:c r="H50" s="9" t="n">
+        <x:v>1.2308532024841794</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="21" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>旅游综合收入</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>对数一阶差分</x:v>
+      </x:c>
+      <x:c r="C51" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E51" s="9" t="n">
+        <x:v>3.333860162413405</x:v>
+      </x:c>
+      <x:c r="F51" s="9" t="n">
+        <x:v>2.70805020110221</x:v>
+      </x:c>
+      <x:c r="G51" s="9" t="n">
+        <x:v>1.2041308405615738</x:v>
+      </x:c>
+      <x:c r="H51" s="9" t="n">
+        <x:v>1.2774828559980613</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2066,19 +3424,19 @@
         <x:v>2026</x:v>
       </x:c>
       <x:c r="B2" t="n">
-        <x:v>224.43130693451835</x:v>
+        <x:v>2906.3520568538356</x:v>
       </x:c>
       <x:c r="C2" t="n">
-        <x:v>173.61813455540295</x:v>
+        <x:v>2401.8353068406677</x:v>
       </x:c>
       <x:c r="D2" t="n">
-        <x:v>279.05169263086566</x:v>
+        <x:v>3366.4764259197964</x:v>
       </x:c>
       <x:c r="E2" t="n">
-        <x:v>125.33333333333331</x:v>
+        <x:v>1781.5669392857153</x:v>
       </x:c>
       <x:c r="F2" t="n">
-        <x:v>290.9090909090906</x:v>
+        <x:v>3486.241273584903</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2086,19 +3444,19 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="B3" t="n">
-        <x:v>251.84705766167988</x:v>
+        <x:v>3138.93804473375</x:v>
       </x:c>
       <x:c r="C3" t="n">
-        <x:v>181.91455386161562</x:v>
+        <x:v>2432.0597844187496</x:v>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>334.5969995162747</x:v>
+        <x:v>3900.9911145776214</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>136.90256410256413</x:v>
+        <x:v>1868.164130763831</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>353.566433566433</x:v>
+        <x:v>4183.489528301885</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2106,19 +3464,19 @@
         <x:v>2028</x:v>
       </x:c>
       <x:c r="B4" t="n">
-        <x:v>282.61182149311907</x:v>
+        <x:v>3390.13713959446</x:v>
       </x:c>
       <x:c r="C4" t="n">
-        <x:v>197.47747601548753</x:v>
+        <x:v>2518.810021322432</x:v>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>394.6405192534152</x:v>
+        <x:v>4520.373753057168</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>134.53556605123794</x:v>
+        <x:v>1846.8652682262345</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>439.5107200261528</x:v>
+        <x:v>4982.8637832413215</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2126,19 +3484,19 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>317.1347022642276</x:v>
+        <x:v>3661.438888397227</x:v>
       </x:c>
       <x:c r="C5" t="n">
-        <x:v>206.68677347144515</x:v>
+        <x:v>2582.6199260176004</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>467.48882549783883</x:v>
+        <x:v>5096.529058813096</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>131.8018331592993</x:v>
+        <x:v>1757.8226777328273</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>536.8294461822715</x:v>
+        <x:v>5751.407153362984</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2146,6 +3504,144 @@
         <x:v>2030</x:v>
       </x:c>
       <x:c r="B6" t="n">
+        <x:v>3954.452041745783</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>2679.0610483781643</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>5725.74378702051</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>1711.7519715612111</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>6635.556261514627</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R574aedc109554013"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>点预测</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>基准下界</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>基准上界</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>压力下界</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>压力上界</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>224.43130693451835</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>173.61813455540295</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>279.05169263086566</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>125.33333333333331</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>290.9090909090906</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>251.84705766167988</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>181.91455386161562</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>334.5969995162747</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>136.90256410256413</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>353.566433566433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>282.61182149311907</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>197.47747601548753</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>394.6405192534152</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>134.53556605123794</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>439.5107200261528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>317.1347022642276</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>206.68677347144515</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>467.48882549783883</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>131.8018331592993</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>536.8294461822715</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
         <x:v>355.8747785172497</x:v>
       </x:c>
       <x:c r="C6" t="n">
@@ -2163,7 +3659,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11026efe760148b7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c6001bbf8c4b55"/>
 </x:worksheet>
 </file>
 
